--- a/public/data/Russian_Daily_Song.xlsx
+++ b/public/data/Russian_Daily_Song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AB7650-6A21-4418-9738-0C5D010FD986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8F9ECB-50EA-4596-A963-705C62DEB600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>SongTitle</t>
   </si>
@@ -46,9 +46,6 @@
     <t>אריק איינשטיין</t>
   </si>
   <si>
-    <t>сидеть на заборе</t>
-  </si>
-  <si>
     <t>Нога здесь, нога там</t>
   </si>
   <si>
@@ -67,8 +64,89 @@
     <t>Я иду.</t>
   </si>
   <si>
-    <t>сидеть на заборе,
+    <t>Сидеть на заборе</t>
+  </si>
+  <si>
+    <t>Сидеть на заборе,
 хорошо со всеми</t>
+  </si>
+  <si>
+    <t>Ты выиграла всё.</t>
+  </si>
+  <si>
+    <t>Я смотрю на тебя,</t>
+  </si>
+  <si>
+    <t>на все, что у тебя есть.</t>
+  </si>
+  <si>
+    <t>אחרי כל השנים</t>
+  </si>
+  <si>
+    <t>עומר אדם</t>
+  </si>
+  <si>
+    <t>Но все это время</t>
+  </si>
+  <si>
+    <t>רביד פלוטניק</t>
+  </si>
+  <si>
+    <t>כל הזמן הזה</t>
+  </si>
+  <si>
+    <t>Я был один.</t>
+  </si>
+  <si>
+    <t>Все это время, каждый день заново</t>
+  </si>
+  <si>
+    <t>כלבויניקית</t>
+  </si>
+  <si>
+    <t>איזי</t>
+  </si>
+  <si>
+    <t>Губы, пара глаз</t>
+  </si>
+  <si>
+    <t>Ямочки на щеках</t>
+  </si>
+  <si>
+    <t>И ее улыбка говорит сама за себя.</t>
+  </si>
+  <si>
+    <t>הכבש השישה עשר</t>
+  </si>
+  <si>
+    <t>גן סגור</t>
+  </si>
+  <si>
+    <t>Вчера в пять часов</t>
+  </si>
+  <si>
+    <t>Мы пошли в магазин с мамой.</t>
+  </si>
+  <si>
+    <t>И по дороге мы увидели, наш сад закрыт.</t>
+  </si>
+  <si>
+    <t>Когда она улыбается</t>
+  </si>
+  <si>
+    <t>הילדה הכי יפה בגן</t>
+  </si>
+  <si>
+    <t>И когда она грустит</t>
+  </si>
+  <si>
+    <t>Я тоже улыбаюсь</t>
+  </si>
+  <si>
+    <t>mchgrIehDT0&amp;list=RDmchgrIehDT0&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -439,70 +517,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="27.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>1982</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2">
-        <v>1982</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>2006</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3">
-        <v>2006</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14">
+        <v>1978</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Daily_Song.xlsx
+++ b/public/data/Russian_Daily_Song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8F9ECB-50EA-4596-A963-705C62DEB600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB12430-C566-4B54-B20D-56B7CCF094AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>SongTitle</t>
   </si>
@@ -143,10 +143,13 @@
     <t>Я тоже улыбаюсь</t>
   </si>
   <si>
-    <t>mchgrIehDT0&amp;list=RDmchgrIehDT0&amp;start_radio=1</t>
-  </si>
-  <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mchgrIehDT0&amp;list=RDmchgrIehDT0&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=uYFx0tkSeEU&amp;list=RDuYFx0tkSeEU&amp;start_radio=1</t>
   </si>
 </sst>
 </file>
@@ -548,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28" x14ac:dyDescent="0.3">
@@ -571,10 +574,10 @@
         <v>1982</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -592,6 +595,9 @@
       </c>
       <c r="F3">
         <v>2006</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">

--- a/public/data/Russian_Daily_Song.xlsx
+++ b/public/data/Russian_Daily_Song.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB12430-C566-4B54-B20D-56B7CCF094AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6FF60E-D90A-42A2-AB30-22D4DBACD9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="230">
   <si>
     <t>SongTitle</t>
   </si>
@@ -116,9 +129,6 @@
     <t>И ее улыбка говорит сама за себя.</t>
   </si>
   <si>
-    <t>הכבש השישה עשר</t>
-  </si>
-  <si>
     <t>גן סגור</t>
   </si>
   <si>
@@ -146,17 +156,581 @@
     <t>Link</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=mchgrIehDT0&amp;list=RDmchgrIehDT0&amp;start_radio=1</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=uYFx0tkSeEU&amp;list=RDuYFx0tkSeEU&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>הסיפור על האיש הירוק</t>
+  </si>
+  <si>
+    <t>איך זה שכוכב</t>
+  </si>
+  <si>
+    <t>מתי כספי</t>
+  </si>
+  <si>
+    <t>לא ידעתי שתלכי ממני</t>
+  </si>
+  <si>
+    <t>בואי</t>
+  </si>
+  <si>
+    <t>גידי גוב</t>
+  </si>
+  <si>
+    <t>אני שוב מתאהב</t>
+  </si>
+  <si>
+    <t>צמוד צמוד</t>
+  </si>
+  <si>
+    <t>שלמה ארצי</t>
+  </si>
+  <si>
+    <t>אבסורד</t>
+  </si>
+  <si>
+    <t>עיר של קיץ</t>
+  </si>
+  <si>
+    <t>ברי סחרוף</t>
+  </si>
+  <si>
+    <t>אהבתיה</t>
+  </si>
+  <si>
+    <t>Однажды зеленым утром встал зеленый человек</t>
+  </si>
+  <si>
+    <t>Он надел на голову зеленую шляпу и вышел на улицу.</t>
+  </si>
+  <si>
+    <t>Он носил зеленые туфли, зеленую рубашку и брюки. Зелень</t>
+  </si>
+  <si>
+    <t>Одна звезда.</t>
+  </si>
+  <si>
+    <t>Я бы не посмел.</t>
+  </si>
+  <si>
+    <t>И я, на самом деле, не одинок.</t>
+  </si>
+  <si>
+    <t>И я сам</t>
+  </si>
+  <si>
+    <t>Как я ненавижу,</t>
+  </si>
+  <si>
+    <t>Как я изменюсь? Для тебя.</t>
+  </si>
+  <si>
+    <t>Дай мне руку и пойдем.</t>
+  </si>
+  <si>
+    <t>Не спрашивайте меня где.</t>
+  </si>
+  <si>
+    <t>Не спрашивай меня о счастье.</t>
+  </si>
+  <si>
+    <t>Игра с сердцем</t>
+  </si>
+  <si>
+    <t>В бессонные ночи</t>
+  </si>
+  <si>
+    <t>Снова выйди в сад.</t>
+  </si>
+  <si>
+    <t>И это делает ее сексуальной.</t>
+  </si>
+  <si>
+    <t>Делает ее красивой</t>
+  </si>
+  <si>
+    <t>Сила глаз, танцы босиком</t>
+  </si>
+  <si>
+    <t>Медленно медленно, а потом быстро быстро.</t>
+  </si>
+  <si>
+    <t>Хочет сильно, сильно дает сильнее. Сильнее, сильнее.</t>
+  </si>
+  <si>
+    <t>И она просит меня выключить какую-то странную песню.</t>
+  </si>
+  <si>
+    <t>Что делать, я больше не знаю,</t>
+  </si>
+  <si>
+    <t>Может быть, есть какой-то секрет,</t>
+  </si>
+  <si>
+    <t>Об этом знают лишь немногие.</t>
+  </si>
+  <si>
+    <t>Вдруг сейчас, вдруг сегодня.</t>
+  </si>
+  <si>
+    <t>Да, теперь она моя.</t>
+  </si>
+  <si>
+    <t>Как в песне,</t>
+  </si>
+  <si>
+    <t>Дни лета или зимы без весны и без осени</t>
+  </si>
+  <si>
+    <t>Я не вернусь к тебе.</t>
+  </si>
+  <si>
+    <t>Это конец, это начало.</t>
+  </si>
+  <si>
+    <t>יוני רכטר</t>
+  </si>
+  <si>
+    <t>הפרויקט של עידן רייכל</t>
+  </si>
+  <si>
+    <t>יהודית רביץ</t>
+  </si>
+  <si>
+    <t>היא רק רוצה לרקוד</t>
+  </si>
+  <si>
+    <t>אהבה</t>
+  </si>
+  <si>
+    <t>דניאל סולומון</t>
+  </si>
+  <si>
+    <t>Она хочет всего того, чем ты был.</t>
+  </si>
+  <si>
+    <t>Она хочет все, что у тебя есть.</t>
+  </si>
+  <si>
+    <t>Она хочет любви.</t>
+  </si>
+  <si>
+    <t>רבות הדרכים</t>
+  </si>
+  <si>
+    <t>Есть много способов любить тебя.</t>
+  </si>
+  <si>
+    <t>Дорога к забвению очень длинная.</t>
+  </si>
+  <si>
+    <t>Мы любили друг друга очень сильно.</t>
+  </si>
+  <si>
+    <t>קמתי לרקוד</t>
+  </si>
+  <si>
+    <t>נינט טייב</t>
+  </si>
+  <si>
+    <t>Это только начало.</t>
+  </si>
+  <si>
+    <t>Немного рук, немного ног</t>
+  </si>
+  <si>
+    <t>Я чуть не встала, чтобы потанцевать.</t>
+  </si>
+  <si>
+    <t>Ждать день и ночь</t>
+  </si>
+  <si>
+    <t>Нет, у меня нет сил прожить еще один день.</t>
+  </si>
+  <si>
+    <t>Розы грустят, а его нет.</t>
+  </si>
+  <si>
+    <t>שושנים עצובות</t>
+  </si>
+  <si>
+    <t>ילדה סוכר</t>
+  </si>
+  <si>
+    <t>מוקי</t>
+  </si>
+  <si>
+    <t>Сахарная девочка</t>
+  </si>
+  <si>
+    <t>Ты уходишь, а я остаюсь.</t>
+  </si>
+  <si>
+    <t>Без тебя у меня ничего нет.</t>
+  </si>
+  <si>
+    <t>Потому что время не останавливается,</t>
+  </si>
+  <si>
+    <t>Летит, горит,</t>
+  </si>
+  <si>
+    <t>дымовая завеса.</t>
+  </si>
+  <si>
+    <t>ילד של אבא</t>
+  </si>
+  <si>
+    <t>עמיר בניון</t>
+  </si>
+  <si>
+    <t>עומד בשער</t>
+  </si>
+  <si>
+    <t>Приходите,</t>
+  </si>
+  <si>
+    <t>мы ждали вас слишком много лет.</t>
+  </si>
+  <si>
+    <t>Мы сошли с ума, у нас больше нет лица.</t>
+  </si>
+  <si>
+    <t>Ты — моя причина улыбаться.</t>
+  </si>
+  <si>
+    <t>Я просто хочу быть рядом с тобой.</t>
+  </si>
+  <si>
+    <t>Ночью и в моих молитвах, может быть, ты придешь ко мне.</t>
+  </si>
+  <si>
+    <t>חלום של כל גבר</t>
+  </si>
+  <si>
+    <t>סאבלימינל</t>
+  </si>
+  <si>
+    <t>לונדון</t>
+  </si>
+  <si>
+    <t>חוה אלברשטיין</t>
+  </si>
+  <si>
+    <t>עורי עור</t>
+  </si>
+  <si>
+    <t>אביב גפן</t>
+  </si>
+  <si>
+    <t>תוצרת הארץ</t>
+  </si>
+  <si>
+    <t>עטור מצחך</t>
+  </si>
+  <si>
+    <t>מגבת באוויר</t>
+  </si>
+  <si>
+    <t>נורוז</t>
+  </si>
+  <si>
+    <t>Она танцует рядом со мной два часа.</t>
+  </si>
+  <si>
+    <t>Танцуй рядом со мной еще два часа.</t>
+  </si>
+  <si>
+    <t>Сабах Аль-Хир, я ем фильмы</t>
+  </si>
+  <si>
+    <t>Но в Лондоне больше фильмов.</t>
+  </si>
+  <si>
+    <t>В Лондоне хорошая музыка.</t>
+  </si>
+  <si>
+    <t>В Лондоне отличное телевидение.</t>
+  </si>
+  <si>
+    <t>Если вы хотели что-то сладкое на праздник</t>
+  </si>
+  <si>
+    <t>Иди выбирай</t>
+  </si>
+  <si>
+    <t>Сделано в Израиле!</t>
+  </si>
+  <si>
+    <t>Любимая родина</t>
+  </si>
+  <si>
+    <t>Потому что мы очень устали.</t>
+  </si>
+  <si>
+    <t>Нужен отдых</t>
+  </si>
+  <si>
+    <t>Послушайте историю о близком и далеком</t>
+  </si>
+  <si>
+    <t>Тебя нравится быть</t>
+  </si>
+  <si>
+    <t>грустным и молчаливым.</t>
+  </si>
+  <si>
+    <t>אף אחד לא בא לי</t>
+  </si>
+  <si>
+    <t>קרולינה</t>
+  </si>
+  <si>
+    <t>Ночами, когда мне холодно</t>
+  </si>
+  <si>
+    <t>Кровать пуста.</t>
+  </si>
+  <si>
+    <t>Почему ты не идёшь?</t>
+  </si>
+  <si>
+    <t>מעליות</t>
+  </si>
+  <si>
+    <t>דודו טסה</t>
+  </si>
+  <si>
+    <t>Но я выше всех.</t>
+  </si>
+  <si>
+    <t>Ничто не трогает</t>
+  </si>
+  <si>
+    <t>Только твой взгляд</t>
+  </si>
+  <si>
+    <t>ניר כנען</t>
+  </si>
+  <si>
+    <t>שיר לנטע</t>
+  </si>
+  <si>
+    <t>Через секунду она видит</t>
+  </si>
+  <si>
+    <t>И знает все.</t>
+  </si>
+  <si>
+    <t>Улыбаешься мне</t>
+  </si>
+  <si>
+    <t>סתלבט בקיבוץ</t>
+  </si>
+  <si>
+    <t>פול טראנק</t>
+  </si>
+  <si>
+    <t>Слушай, ты живешь далеко.</t>
+  </si>
+  <si>
+    <t>Насколько это стрессово, так почему же город?</t>
+  </si>
+  <si>
+    <t>Правильно, брат, я живу далеко, от тебя.</t>
+  </si>
+  <si>
+    <t>Дай ему шанс,</t>
+  </si>
+  <si>
+    <t>Он поет от всего сердца.</t>
+  </si>
+  <si>
+    <t>От всего сердца, от всего сердца</t>
+  </si>
+  <si>
+    <t>מה קשור</t>
+  </si>
+  <si>
+    <t>תנו לו צ'אנס</t>
+  </si>
+  <si>
+    <t>כל החברים שלך</t>
+  </si>
+  <si>
+    <t>אנה זק</t>
+  </si>
+  <si>
+    <t>Как пиво, когда оно горячее.</t>
+  </si>
+  <si>
+    <t>Все твои друзья любят меня больше, чем тебя.</t>
+  </si>
+  <si>
+    <t>Почиволи в море.</t>
+  </si>
+  <si>
+    <t>זה בדם שלי</t>
+  </si>
+  <si>
+    <t>יסמין מועלם</t>
+  </si>
+  <si>
+    <t>Я никуда не бегу, я Шанти.</t>
+  </si>
+  <si>
+    <t>Это у меня в крови. Это у меня в крови. Это у меня в крови.</t>
+  </si>
+  <si>
+    <t>Нет, это не ошибка. Я здесь потому что</t>
+  </si>
+  <si>
+    <t>Я вообще ни о ком не думаю.</t>
+  </si>
+  <si>
+    <t>את</t>
+  </si>
+  <si>
+    <t>עטר מיינר</t>
+  </si>
+  <si>
+    <t>Мне нравится, какой ты есть.</t>
+  </si>
+  <si>
+    <t>Ты, ты, ты, ты, ты</t>
+  </si>
+  <si>
+    <t>JNwJFLkoX80&amp;list=RDJNwJFLkoX80&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>cWNrbJl51AA&amp;list=RDcWNrbJl51AA&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>m5HXWKvKN5Y&amp;list=RDm5HXWKvKN5Y&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>Ey_K97x15ek&amp;list=RDEy_K97x15ek&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>VrnMA9YinRY&amp;list=RDVrnMA9YinRY&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>4ok4io20xvc&amp;list=RD4ok4io20xvc&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>I-i9Byoj_pk&amp;list=RDI-i9Byoj_pk&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>CJmMpc0lo1c&amp;list=RDCJmMpc0lo1c&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>osnEGXT3SvQ&amp;list=RDosnEGXT3SvQ&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>gXTHdj3Vw3s&amp;list=RDgXTHdj3Vw3s&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>_uJLsc05ZE4&amp;list=RD_uJLsc05ZE4&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>qoGurrdtz6Q&amp;list=RDqoGurrdtz6Q&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>bhNYlOt00uw&amp;list=RDbhNYlOt00uw&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>h0SuqxOe1Bs&amp;list=RDh0SuqxOe1Bs&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>dFqAtitDNvs&amp;list=RDdFqAtitDNvs&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>fNThHjoimrY&amp;list=RDfNThHjoimrY&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>19qoWmBJVRc</t>
+  </si>
+  <si>
+    <t>TYIrff9kP4M&amp;t=2s</t>
+  </si>
+  <si>
+    <t>אהובתי כבר לא רואה אותי</t>
+  </si>
+  <si>
+    <t>Всегда люблю тебя очень сильно.</t>
+  </si>
+  <si>
+    <t>Ты снова играл с моими чувствами.</t>
+  </si>
+  <si>
+    <t>Почему я это заслужил?</t>
+  </si>
+  <si>
+    <t>UGiAYMyCcIA</t>
+  </si>
+  <si>
+    <t>CeyDkESf-Ko&amp;list=RDCeyDkESf-Ko&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>mL9ngehXhH0&amp;list=RDmL9ngehXhH0&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>egtOB8arAN0&amp;list=RDegtOB8arAN0&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>5fP6hryNTug&amp;list=RD5fP6hryNTug&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>aCuOpK6ECUQ&amp;list=RDaCuOpK6ECUQ&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>wKF6wM7IN0I&amp;list=RDwKF6wM7IN0I&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>4vH98hkgD7Y&amp;list=RD4vH98hkgD7Y&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>NdU4hDYVmvY&amp;list=RDNdU4hDYVmvY&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>ZPwhMykB_-Q&amp;list=RDZPwhMykB_-Q&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>QgsLpE4ULfA&amp;list=RDQgsLpE4ULfA&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>X6rsfFU6J1o&amp;list=RDX6rsfFU6J1o&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>5_5PtfmoIQk&amp;list=RD5_5PtfmoIQk&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>NwsNCqvPUhk&amp;list=RDNwsNCqvPUhk&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>wcayUsa9yvw&amp;list=RDwcayUsa9yvw&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>yjE8RgR4m-c</t>
+  </si>
+  <si>
+    <t>_Oeh7FpUN6Q&amp;list=RD_Oeh7FpUN6Q&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>0sWkhy35ddA&amp;list=RD0sWkhy35ddA&amp;start_radio=1</t>
+  </si>
+  <si>
+    <t>gS4FzpRKxkc</t>
+  </si>
+  <si>
+    <t>ajN_M2k_STM&amp;list=RDajN_M2k_STM&amp;start_radio=1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +744,22 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="177"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -205,10 +795,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -216,9 +807,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="היפר-קישור" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -520,15 +1118,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.08203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.08203125" customWidth="1"/>
+    <col min="1" max="1" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.5" customWidth="1"/>
+    <col min="5" max="5" width="53.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="71.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -551,7 +1149,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28" x14ac:dyDescent="0.3">
@@ -573,11 +1171,11 @@
       <c r="F2">
         <v>1982</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="28" x14ac:dyDescent="0.3">
+      <c r="G2" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -597,7 +1195,7 @@
         <v>2006</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -619,6 +1217,9 @@
       <c r="F4">
         <v>2016</v>
       </c>
+      <c r="G4" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -639,6 +1240,9 @@
       <c r="F5">
         <v>2017</v>
       </c>
+      <c r="G5" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -659,48 +1263,796 @@
       <c r="F6">
         <v>2011</v>
       </c>
+      <c r="G6" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>35</v>
       </c>
       <c r="F7">
         <v>1978</v>
       </c>
+      <c r="G7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8">
+        <v>1978</v>
+      </c>
+      <c r="G8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9">
+        <v>1974</v>
+      </c>
+      <c r="G9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10">
+        <v>1976</v>
+      </c>
+      <c r="G10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11">
+        <v>2002</v>
+      </c>
+      <c r="G11" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12">
+        <v>1991</v>
+      </c>
+      <c r="G12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13">
+        <v>1978</v>
+      </c>
+      <c r="G13" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F14">
-        <v>1978</v>
+        <v>2015</v>
+      </c>
+      <c r="G14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15">
+        <v>2024</v>
+      </c>
+      <c r="G15" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16">
+        <v>1996</v>
+      </c>
+      <c r="G16" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17">
+        <v>1970</v>
+      </c>
+      <c r="G17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18">
+        <v>1998</v>
+      </c>
+      <c r="G18" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19">
+        <v>2005</v>
+      </c>
+      <c r="G19" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20">
+        <v>2021</v>
+      </c>
+      <c r="G20" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21">
+        <v>2012</v>
+      </c>
+      <c r="G21" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22">
+        <v>2001</v>
+      </c>
+      <c r="G22" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23">
+        <v>2005</v>
+      </c>
+      <c r="G23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24">
+        <v>2018</v>
+      </c>
+      <c r="G24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25">
+        <v>2015</v>
+      </c>
+      <c r="G25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26">
+        <v>1989</v>
+      </c>
+      <c r="G26" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27">
+        <v>2000</v>
+      </c>
+      <c r="G27" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28">
+        <v>2014</v>
+      </c>
+      <c r="G28" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29">
+        <v>1985</v>
+      </c>
+      <c r="G29" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" t="s">
+        <v>135</v>
+      </c>
+      <c r="F30">
+        <v>2020</v>
+      </c>
+      <c r="G30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" t="s">
+        <v>151</v>
+      </c>
+      <c r="E31" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31">
+        <v>2009</v>
+      </c>
+      <c r="G31" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32">
+        <v>1988</v>
+      </c>
+      <c r="G32" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33">
+        <v>2006</v>
+      </c>
+      <c r="G33" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>158</v>
+      </c>
+      <c r="B34" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" t="s">
+        <v>162</v>
+      </c>
+      <c r="F34">
+        <v>2024</v>
+      </c>
+      <c r="G34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" t="s">
+        <v>166</v>
+      </c>
+      <c r="F35">
+        <v>2022</v>
+      </c>
+      <c r="G35" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" t="s">
+        <v>172</v>
+      </c>
+      <c r="C36" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" t="s">
+        <v>169</v>
+      </c>
+      <c r="E36" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36">
+        <v>2009</v>
+      </c>
+      <c r="G36" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" t="s">
+        <v>175</v>
+      </c>
+      <c r="D37" t="s">
+        <v>177</v>
+      </c>
+      <c r="E37" t="s">
+        <v>176</v>
+      </c>
+      <c r="F37">
+        <v>2021</v>
+      </c>
+      <c r="G37" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D38" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" t="s">
+        <v>181</v>
+      </c>
+      <c r="F38">
+        <v>2020</v>
+      </c>
+      <c r="G38" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>185</v>
+      </c>
+      <c r="B39" t="s">
+        <v>184</v>
+      </c>
+      <c r="C39" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" t="s">
+        <v>186</v>
+      </c>
+      <c r="E39" t="s">
+        <v>187</v>
+      </c>
+      <c r="F39">
+        <v>2018</v>
+      </c>
+      <c r="G39" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" t="s">
+        <v>208</v>
+      </c>
+      <c r="E40" t="s">
+        <v>209</v>
+      </c>
+      <c r="F40">
+        <v>2024</v>
+      </c>
+      <c r="G40" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{498D4A10-4E22-4E16-9780-BA5F290A4C3E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/data/Russian_Daily_Song.xlsx
+++ b/public/data/Russian_Daily_Song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A35D114-4AE5-4029-99C7-A35B67432821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAE088D-F8E7-4172-9A8C-7FCD321D8CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,9 +149,6 @@
     <t>Link</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=uYFx0tkSeEU&amp;list=RDuYFx0tkSeEU&amp;start_radio=1</t>
-  </si>
-  <si>
     <t>הסיפור על האיש הירוק</t>
   </si>
   <si>
@@ -724,6 +721,9 @@
   <si>
     <t>Сижу на заборе,
 хорошо со всеми</t>
+  </si>
+  <si>
+    <t>uYFx0tkSeEU&amp;list=RDuYFx0tkSeEU&amp;start_radio=1</t>
   </si>
 </sst>
 </file>
@@ -1160,19 +1160,19 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F2">
         <v>1982</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>38</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1195,7 +1195,7 @@
         <v>2006</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1218,7 +1218,7 @@
         <v>2016</v>
       </c>
       <c r="G4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1241,7 +1241,7 @@
         <v>2017</v>
       </c>
       <c r="G5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1264,12 +1264,12 @@
         <v>2011</v>
       </c>
       <c r="G6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
@@ -1287,127 +1287,127 @@
         <v>1978</v>
       </c>
       <c r="G7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" t="s">
         <v>52</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" t="s">
-        <v>53</v>
       </c>
       <c r="F8">
         <v>1978</v>
       </c>
       <c r="G8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
         <v>55</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>56</v>
-      </c>
-      <c r="E9" t="s">
-        <v>57</v>
       </c>
       <c r="F9">
         <v>1974</v>
       </c>
       <c r="G9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
       <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
         <v>58</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="F10">
         <v>1976</v>
       </c>
       <c r="G10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
         <v>61</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>62</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
       </c>
       <c r="F11">
         <v>2002</v>
       </c>
       <c r="G11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
         <v>44</v>
       </c>
-      <c r="B12" t="s">
-        <v>45</v>
-      </c>
       <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" t="s">
         <v>64</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>66</v>
       </c>
       <c r="F12">
         <v>1991</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -1425,7 +1425,7 @@
         <v>1978</v>
       </c>
       <c r="G13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1433,22 +1433,22 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
         <v>67</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>68</v>
-      </c>
-      <c r="E14" t="s">
-        <v>69</v>
       </c>
       <c r="F14">
         <v>2015</v>
       </c>
       <c r="G14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1456,321 +1456,321 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" t="s">
         <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>72</v>
       </c>
       <c r="F15">
         <v>2024</v>
       </c>
       <c r="G15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
         <v>47</v>
       </c>
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
       <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
         <v>73</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>74</v>
-      </c>
-      <c r="E16" t="s">
-        <v>75</v>
       </c>
       <c r="F16">
         <v>1996</v>
       </c>
       <c r="G16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" t="s">
         <v>76</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>78</v>
       </c>
       <c r="F17">
         <v>1970</v>
       </c>
       <c r="G17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" t="s">
         <v>79</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>80</v>
-      </c>
-      <c r="E18" t="s">
-        <v>81</v>
       </c>
       <c r="F18">
         <v>1998</v>
       </c>
       <c r="G18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
         <v>87</v>
       </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>88</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>89</v>
-      </c>
-      <c r="E19" t="s">
-        <v>90</v>
       </c>
       <c r="F19">
         <v>2005</v>
       </c>
       <c r="G19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
         <v>96</v>
       </c>
-      <c r="B20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>97</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>98</v>
-      </c>
-      <c r="E20" t="s">
-        <v>99</v>
       </c>
       <c r="F20">
         <v>2021</v>
       </c>
       <c r="G20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
         <v>100</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>101</v>
-      </c>
-      <c r="E21" t="s">
-        <v>102</v>
       </c>
       <c r="F21">
         <v>2012</v>
       </c>
       <c r="G21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
         <v>105</v>
       </c>
-      <c r="B22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>106</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>107</v>
-      </c>
-      <c r="E22" t="s">
-        <v>108</v>
       </c>
       <c r="F22">
         <v>2001</v>
       </c>
       <c r="G22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
         <v>91</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>92</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>93</v>
-      </c>
-      <c r="E23" t="s">
-        <v>94</v>
       </c>
       <c r="F23">
         <v>2005</v>
       </c>
       <c r="G23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" t="s">
         <v>113</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>114</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>115</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>116</v>
-      </c>
-      <c r="E24" t="s">
-        <v>117</v>
       </c>
       <c r="F24">
         <v>2018</v>
       </c>
       <c r="G24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" t="s">
         <v>118</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>119</v>
-      </c>
-      <c r="E25" t="s">
-        <v>120</v>
       </c>
       <c r="F25">
         <v>2015</v>
       </c>
       <c r="G25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" t="s">
         <v>134</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>135</v>
-      </c>
-      <c r="E26" t="s">
-        <v>136</v>
       </c>
       <c r="F26">
         <v>1989</v>
       </c>
       <c r="G26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" t="s">
         <v>140</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>141</v>
-      </c>
-      <c r="E27" t="s">
-        <v>142</v>
       </c>
       <c r="F27">
         <v>2000</v>
       </c>
       <c r="G27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" t="s">
         <v>109</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>110</v>
-      </c>
-      <c r="E28" t="s">
-        <v>111</v>
       </c>
       <c r="F28">
         <v>2014</v>
       </c>
       <c r="G28" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1778,68 +1778,68 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" t="s">
         <v>137</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>138</v>
-      </c>
-      <c r="E29" t="s">
-        <v>139</v>
       </c>
       <c r="F29">
         <v>1985</v>
       </c>
       <c r="G29" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" t="s">
         <v>130</v>
       </c>
-      <c r="B30" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>131</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>132</v>
-      </c>
-      <c r="E30" t="s">
-        <v>133</v>
       </c>
       <c r="F30">
         <v>2020</v>
       </c>
       <c r="G30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" t="s">
         <v>147</v>
       </c>
-      <c r="B31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>148</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>149</v>
-      </c>
-      <c r="E31" t="s">
-        <v>150</v>
       </c>
       <c r="F31">
         <v>2009</v>
       </c>
       <c r="G31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1847,183 +1847,183 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" t="s">
         <v>144</v>
       </c>
-      <c r="D32" t="s">
-        <v>145</v>
-      </c>
       <c r="E32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F32">
         <v>1988</v>
       </c>
       <c r="G32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" t="s">
         <v>152</v>
       </c>
-      <c r="B33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>153</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>154</v>
-      </c>
-      <c r="E33" t="s">
-        <v>155</v>
       </c>
       <c r="F33">
         <v>2006</v>
       </c>
       <c r="G33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" t="s">
         <v>156</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>157</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>158</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>159</v>
-      </c>
-      <c r="E34" t="s">
-        <v>160</v>
       </c>
       <c r="F34">
         <v>2024</v>
       </c>
       <c r="G34" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" t="s">
         <v>162</v>
       </c>
-      <c r="B35" t="s">
-        <v>161</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>164</v>
+      </c>
+      <c r="E35" t="s">
         <v>163</v>
-      </c>
-      <c r="D35" t="s">
-        <v>165</v>
-      </c>
-      <c r="E35" t="s">
-        <v>164</v>
       </c>
       <c r="F35">
         <v>2022</v>
       </c>
       <c r="G35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" t="s">
         <v>169</v>
       </c>
-      <c r="B36" t="s">
-        <v>170</v>
-      </c>
       <c r="C36" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" t="s">
         <v>166</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>167</v>
-      </c>
-      <c r="E36" t="s">
-        <v>168</v>
       </c>
       <c r="F36">
         <v>2009</v>
       </c>
       <c r="G36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>171</v>
+      </c>
+      <c r="B37" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37" t="s">
         <v>172</v>
       </c>
-      <c r="B37" t="s">
-        <v>171</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
+        <v>174</v>
+      </c>
+      <c r="E37" t="s">
         <v>173</v>
-      </c>
-      <c r="D37" t="s">
-        <v>175</v>
-      </c>
-      <c r="E37" t="s">
-        <v>174</v>
       </c>
       <c r="F37">
         <v>2021</v>
       </c>
       <c r="G37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>176</v>
+      </c>
+      <c r="B38" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" t="s">
         <v>177</v>
       </c>
-      <c r="B38" t="s">
-        <v>176</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>179</v>
+      </c>
+      <c r="E38" t="s">
         <v>178</v>
-      </c>
-      <c r="D38" t="s">
-        <v>180</v>
-      </c>
-      <c r="E38" t="s">
-        <v>179</v>
       </c>
       <c r="F38">
         <v>2020</v>
       </c>
       <c r="G38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" t="s">
+        <v>181</v>
+      </c>
+      <c r="C39" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" t="s">
         <v>183</v>
       </c>
-      <c r="B39" t="s">
-        <v>182</v>
-      </c>
-      <c r="C39" t="s">
-        <v>181</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>184</v>
-      </c>
-      <c r="E39" t="s">
-        <v>185</v>
       </c>
       <c r="F39">
         <v>2018</v>
       </c>
       <c r="G39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2031,27 +2031,27 @@
         <v>18</v>
       </c>
       <c r="B40" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" t="s">
         <v>204</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>205</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>206</v>
-      </c>
-      <c r="E40" t="s">
-        <v>207</v>
       </c>
       <c r="F40">
         <v>2024</v>
       </c>
       <c r="G40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{498D4A10-4E22-4E16-9780-BA5F290A4C3E}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.youtube.com/watch?v=uYFx0tkSeEU&amp;list=RDuYFx0tkSeEU&amp;start_radio=1" xr:uid="{498D4A10-4E22-4E16-9780-BA5F290A4C3E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
